--- a/data/trans_camb/P45C_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P45C_R2-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 11,91</t>
+          <t>-0,44; 12,12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 13,63</t>
+          <t>0,96; 14,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,82; -8,79</t>
+          <t>-16,57; -8,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 4,69</t>
+          <t>-7,45; 5,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 5,61</t>
+          <t>-6,24; 5,94</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-18,77; -10,36</t>
+          <t>-19,48; -10,44</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 7,32</t>
+          <t>-1,63; 6,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 8,51</t>
+          <t>-0,45; 8,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,42; -10,46</t>
+          <t>-16,57; -10,37</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 126,12</t>
+          <t>-4,02; 131,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 143,75</t>
+          <t>4,79; 144,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-40,81; 39,92</t>
+          <t>-41,96; 44,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,96; 49,99</t>
+          <t>-34,71; 49,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -93,83</t>
+          <t>-100,0; -93,84</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 64,78</t>
+          <t>-11,47; 59,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 79,45</t>
+          <t>-4,79; 71,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -96,31</t>
+          <t>-100,0; -95,89</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,53; -6,83</t>
+          <t>-16,44; -6,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,07; -6,72</t>
+          <t>-16,29; -6,13</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,57; -0,47</t>
+          <t>-12,8; -0,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,4; -5,43</t>
+          <t>-14,51; -5,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,09; -0,65</t>
+          <t>-10,08; -0,85</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 0,68</t>
+          <t>-8,51; 0,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,24; -7,79</t>
+          <t>-14,26; -7,57</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,73; -5,04</t>
+          <t>-11,77; -5,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,11; -1,75</t>
+          <t>-9,06; -1,24</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-62,55; -32,0</t>
+          <t>-61,96; -31,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-59,59; -31,16</t>
+          <t>-60,52; -28,91</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-46,54; -0,38</t>
+          <t>-47,21; 0,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-64,5; -29,93</t>
+          <t>-64,01; -32,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,86; -3,55</t>
+          <t>-44,09; -3,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-39,08; 5,34</t>
+          <t>-38,71; 6,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-60,3; -38,31</t>
+          <t>-60,26; -38,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-48,7; -24,19</t>
+          <t>-49,01; -24,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-38,3; -8,47</t>
+          <t>-38,07; -6,14</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,21; 24,09</t>
+          <t>11,62; 23,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 1,49</t>
+          <t>-8,21; 1,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,1; -1,55</t>
+          <t>-11,19; -1,64</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,02; 10,84</t>
+          <t>0,16; 10,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 6,11</t>
+          <t>-4,05; 5,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,34; 0,54</t>
+          <t>-8,06; 0,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,16; 15,37</t>
+          <t>7,18; 15,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 2,43</t>
+          <t>-4,35; 2,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,13; -1,87</t>
+          <t>-8,3; -1,76</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>66,85; 240,56</t>
+          <t>71,04; 240,21</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,08; 15,39</t>
+          <t>-56,41; 18,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-71,74; -13,23</t>
+          <t>-70,63; -11,99</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,05; 122,41</t>
+          <t>1,26; 120,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-28,22; 74,32</t>
+          <t>-29,43; 69,47</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-59,73; 5,78</t>
+          <t>-58,21; 9,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50,02; 155,0</t>
+          <t>49,73; 152,43</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-34,52; 23,55</t>
+          <t>-33,01; 23,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-58,43; -17,78</t>
+          <t>-60,66; -17,39</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,27; -4,71</t>
+          <t>-16,3; -4,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,98; -3,01</t>
+          <t>-14,92; -2,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,34; 1,21</t>
+          <t>-14,6; 1,07</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,95; -0,2</t>
+          <t>-9,07; -0,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 3,35</t>
+          <t>-6,3; 3,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-8,76; 0,89</t>
+          <t>-9,14; 0,55</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,86; -3,85</t>
+          <t>-10,68; -3,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,91; -1,58</t>
+          <t>-8,72; -1,07</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,99; -2,28</t>
+          <t>-10,95; -2,01</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-62,49; -23,52</t>
+          <t>-62,0; -22,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-57,55; -14,92</t>
+          <t>-57,86; -14,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-57,97; 9,91</t>
+          <t>-58,95; 6,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-58,2; 1,93</t>
+          <t>-60,3; -1,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-38,07; 33,27</t>
+          <t>-42,17; 31,93</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-59,05; 6,55</t>
+          <t>-59,91; 4,6</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-56,36; -25,08</t>
+          <t>-55,35; -22,67</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-45,32; -9,53</t>
+          <t>-44,3; -6,35</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-55,96; -13,89</t>
+          <t>-57,36; -11,99</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,04; 10,99</t>
+          <t>0,11; 10,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 2,33</t>
+          <t>-6,42; 1,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 4,37</t>
+          <t>-4,25; 4,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 10,03</t>
+          <t>-0,4; 10,16</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-10,22; -3,23</t>
+          <t>-9,83; -3,16</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 1,64</t>
+          <t>-6,57; 1,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,5; 8,79</t>
+          <t>1,3; 8,65</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,92; -1,75</t>
+          <t>-6,97; -1,78</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 1,7</t>
+          <t>-4,48; 1,48</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 327,43</t>
+          <t>-8,99; 288,82</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-77,97; 108,06</t>
+          <t>-79,46; 75,13</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-55,46; 127,82</t>
+          <t>-57,09; 128,86</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 240,14</t>
+          <t>-6,48; 239,68</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -61,5</t>
+          <t>-100,0; -65,53</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-73,15; 44,13</t>
+          <t>-73,23; 50,52</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>15,89; 197,55</t>
+          <t>13,95; 200,44</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-87,53; -33,77</t>
+          <t>-88,79; -36,58</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-54,23; 40,89</t>
+          <t>-55,82; 36,98</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,53; 14,77</t>
+          <t>-0,74; 14,95</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-30,13; -18,11</t>
+          <t>-29,01; -18,35</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-10,14; 4,36</t>
+          <t>-9,96; 4,13</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,45; 13,25</t>
+          <t>0,22; 13,44</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-17,61; -7,71</t>
+          <t>-16,97; -7,43</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,65; 18,78</t>
+          <t>6,08; 19,19</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,21; 12,31</t>
+          <t>2,0; 12,73</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-21,64; -14,02</t>
+          <t>-21,93; -13,9</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,39; 9,61</t>
+          <t>-0,42; 9,77</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 70,1</t>
+          <t>-2,73; 67,4</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-97,05; -81,72</t>
+          <t>-96,85; -80,56</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-35,43; 20,3</t>
+          <t>-34,63; 17,97</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1,82; 101,08</t>
+          <t>2,49; 107,42</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-86,88; -50,42</t>
+          <t>-87,31; -53,93</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>32,64; 141,03</t>
+          <t>32,33; 148,62</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,97; 66,24</t>
+          <t>8,63; 67,89</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-91,22; -75,41</t>
+          <t>-90,8; -75,04</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1,76; 52,71</t>
+          <t>-1,98; 54,4</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>7,95; 16,98</t>
+          <t>8,7; 17,03</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 5,31</t>
+          <t>-2,68; 5,35</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 4,96</t>
+          <t>-3,81; 5,2</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7,64; 15,43</t>
+          <t>7,87; 15,8</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,89; 9,88</t>
+          <t>2,61; 9,71</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 4,76</t>
+          <t>-7,06; 4,92</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,94; 15,26</t>
+          <t>8,96; 15,18</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,32; 6,7</t>
+          <t>1,03; 6,7</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 3,35</t>
+          <t>-5,32; 3,34</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>52,29; 155,45</t>
+          <t>55,66; 151,89</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-18,48; 48,65</t>
+          <t>-18,8; 48,42</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-24,79; 44,44</t>
+          <t>-24,97; 48,48</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>66,61; 190,5</t>
+          <t>65,36; 191,25</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>25,29; 121,67</t>
+          <t>21,29; 113,66</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-58,23; 52,96</t>
+          <t>-57,82; 52,96</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>69,69; 151,2</t>
+          <t>70,34; 151,12</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>9,58; 66,56</t>
+          <t>8,18; 66,97</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-40,86; 31,46</t>
+          <t>-41,93; 31,36</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 0,13</t>
+          <t>-5,9; -0,15</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>4,89; 11,88</t>
+          <t>4,97; 12,12</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 23,12</t>
+          <t>-0,15; 23,15</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 0,76</t>
+          <t>-4,74; 0,46</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>5,55; 12,51</t>
+          <t>5,73; 12,84</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,39; 12,02</t>
+          <t>5,88; 12,31</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,61; -0,54</t>
+          <t>-4,53; -0,66</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>6,19; 11,31</t>
+          <t>6,31; 11,53</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>1,49; 15,87</t>
+          <t>2,83; 15,9</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-48,91; 1,72</t>
+          <t>-48,72; -1,66</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>38,88; 132,54</t>
+          <t>41,1; 133,16</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 230,23</t>
+          <t>2,49; 228,19</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-45,14; 10,42</t>
+          <t>-45,19; 6,14</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>50,93; 162,57</t>
+          <t>48,42; 159,73</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>50,19; 155,06</t>
+          <t>53,83; 157,96</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-40,67; -5,2</t>
+          <t>-41,27; -6,94</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>55,51; 126,65</t>
+          <t>57,18; 128,39</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>24,03; 168,01</t>
+          <t>25,79; 167,81</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,08; 3,82</t>
+          <t>0,05; 3,55</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-4,09; -0,44</t>
+          <t>-4,13; -0,51</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 2,07</t>
+          <t>-3,68; 2,04</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 2,72</t>
+          <t>-0,62; 2,69</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,78</t>
+          <t>-0,57; 2,7</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 1,59</t>
+          <t>-2,82; 1,64</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,2; 2,66</t>
+          <t>0,3; 2,69</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 0,76</t>
+          <t>-1,69; 0,71</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 1,24</t>
+          <t>-2,23; 1,28</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0,47; 25,95</t>
+          <t>0,36; 23,88</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-24,69; -2,96</t>
+          <t>-24,68; -3,25</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-21,6; 13,83</t>
+          <t>-22,86; 13,27</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 23,21</t>
+          <t>-4,9; 22,97</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 23,87</t>
+          <t>-4,8; 22,52</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-20,04; 13,29</t>
+          <t>-21,58; 14,04</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>1,31; 19,87</t>
+          <t>2,17; 20,01</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-12,3; 5,63</t>
+          <t>-11,48; 5,31</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-15,5; 9,04</t>
+          <t>-15,6; 9,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P45C_R2-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P45C_R2-Provincia-trans_camb.xlsx
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-14,47</t>
+          <t>-14,49</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 12,12</t>
+          <t>-0,19; 12,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,96; 14,16</t>
+          <t>1,18; 14,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-16,57; -8,43</t>
+          <t>-16,85; -8,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 5,11</t>
+          <t>-7,21; 5,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,24; 5,94</t>
+          <t>-5,93; 5,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-19,48; -10,44</t>
+          <t>-19,1; -10,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 6,94</t>
+          <t>-2,23; 6,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 8,3</t>
+          <t>-1,55; 7,67</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-16,57; -10,37</t>
+          <t>-16,72; -10,67</t>
         </is>
       </c>
     </row>
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-98,79%</t>
+          <t>-98,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-99,37%</t>
+          <t>-99,42%</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,02; 131,09</t>
+          <t>-2,26; 121,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>4,79; 144,85</t>
+          <t>6,42; 145,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-41,96; 44,71</t>
+          <t>-41,59; 46,2</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-34,71; 49,93</t>
+          <t>-33,57; 51,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -93,84</t>
+          <t>-100,0; -94,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-11,47; 59,34</t>
+          <t>-14,76; 57,47</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 71,33</t>
+          <t>-9,91; 65,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -95,89</t>
+          <t>-100,0; -97,12</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-6,55</t>
+          <t>-6,94</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-4,16</t>
+          <t>-4,42</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-5,33</t>
+          <t>-5,67</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-16,44; -6,91</t>
+          <t>-16,69; -7,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,29; -6,13</t>
+          <t>-16,36; -6,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,8; -0,09</t>
+          <t>-13,15; -1,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-14,51; -5,91</t>
+          <t>-14,3; -5,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,08; -0,85</t>
+          <t>-9,8; -0,73</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-8,51; 0,91</t>
+          <t>-9,6; 0,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,26; -7,57</t>
+          <t>-14,15; -7,77</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-11,77; -5,04</t>
+          <t>-11,67; -4,88</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-9,06; -1,24</t>
+          <t>-9,12; -2,09</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-27,17%</t>
+          <t>-28,81%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-20,83%</t>
+          <t>-22,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-24,21%</t>
+          <t>-25,78%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-61,96; -31,75</t>
+          <t>-62,81; -32,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-60,52; -28,91</t>
+          <t>-60,74; -29,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-47,21; 0,76</t>
+          <t>-49,35; -6,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-64,01; -32,89</t>
+          <t>-64,09; -30,85</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-44,09; -3,82</t>
+          <t>-44,15; -3,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-38,71; 6,12</t>
+          <t>-41,6; 1,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-60,26; -38,04</t>
+          <t>-59,89; -38,4</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-49,01; -24,63</t>
+          <t>-49,05; -23,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-38,07; -6,14</t>
+          <t>-38,59; -10,21</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-6,29</t>
+          <t>-5,7</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-3,74</t>
+          <t>-3,92</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-4,96</t>
+          <t>-4,78</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,62; 23,75</t>
+          <t>11,33; 23,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,21; 1,79</t>
+          <t>-8,36; 1,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,19; -1,64</t>
+          <t>-10,56; -1,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,16; 10,94</t>
+          <t>-0,21; 10,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 5,93</t>
+          <t>-3,67; 5,69</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 0,74</t>
+          <t>-8,19; 0,45</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,18; 15,41</t>
+          <t>7,11; 15,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 2,35</t>
+          <t>-4,54; 2,18</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-8,3; -1,76</t>
+          <t>-7,64; -1,65</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-50,1%</t>
+          <t>-45,42%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-32,76%</t>
+          <t>-34,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-41,47%</t>
+          <t>-39,92%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>71,04; 240,21</t>
+          <t>70,31; 250,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-56,41; 18,09</t>
+          <t>-54,53; 18,53</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-70,63; -11,99</t>
+          <t>-68,95; -8,94</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,26; 120,28</t>
+          <t>-2,67; 117,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-29,43; 69,47</t>
+          <t>-27,69; 63,5</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-58,21; 9,23</t>
+          <t>-59,58; 6,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>49,73; 152,43</t>
+          <t>52,23; 154,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,01; 23,09</t>
+          <t>-33,15; 21,82</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-60,66; -17,39</t>
+          <t>-56,75; -14,16</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-8,03</t>
+          <t>-7,97</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-3,68</t>
+          <t>-1,49</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-6,38</t>
+          <t>-4,76</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-16,3; -4,87</t>
+          <t>-16,16; -4,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-14,92; -2,72</t>
+          <t>-15,0; -3,9</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 1,07</t>
+          <t>-14,55; -0,88</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-9,07; -0,17</t>
+          <t>-8,86; -0,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 3,5</t>
+          <t>-6,09; 3,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 0,55</t>
+          <t>-6,23; 3,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-10,68; -3,58</t>
+          <t>-11,12; -3,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,72; -1,07</t>
+          <t>-8,76; -1,38</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-10,95; -2,01</t>
+          <t>-8,93; -0,44</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-35,31%</t>
+          <t>-35,02%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-29,15%</t>
+          <t>-11,78%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-36,22%</t>
+          <t>-27,02%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-62,0; -22,23</t>
+          <t>-61,46; -19,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-57,86; -14,13</t>
+          <t>-58,22; -18,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-58,95; 6,18</t>
+          <t>-57,7; -1,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-60,3; -1,55</t>
+          <t>-60,24; -0,09</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-42,17; 31,93</t>
+          <t>-41,32; 33,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-59,91; 4,6</t>
+          <t>-39,64; 31,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-55,35; -22,67</t>
+          <t>-57,02; -23,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-44,3; -6,35</t>
+          <t>-45,14; -8,96</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-57,36; -11,99</t>
+          <t>-45,71; -2,67</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-2,35</t>
+          <t>-2,77</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-1,28</t>
+          <t>-1,26</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,11; 10,68</t>
+          <t>0,27; 10,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 1,65</t>
+          <t>-6,02; 2,07</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 4,22</t>
+          <t>-3,9; 4,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 10,16</t>
+          <t>-1,1; 10,08</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,83; -3,16</t>
+          <t>-10,1; -3,15</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 1,77</t>
+          <t>-6,82; 1,26</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,3; 8,65</t>
+          <t>1,19; 8,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,97; -1,78</t>
+          <t>-6,79; -1,48</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 1,48</t>
+          <t>-4,0; 1,84</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-1,78%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-36,25%</t>
+          <t>-42,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-21,2%</t>
+          <t>-20,79%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 288,82</t>
+          <t>-4,74; 290,16</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-79,46; 75,13</t>
+          <t>-79,74; 71,11</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-57,09; 128,86</t>
+          <t>-52,34; 149,93</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 239,68</t>
+          <t>-16,23; 227,11</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -65,53</t>
+          <t>-100,0; -58,89</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-73,23; 50,52</t>
+          <t>-73,67; 39,81</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,95; 200,44</t>
+          <t>14,68; 202,75</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-88,79; -36,58</t>
+          <t>-88,3; -25,67</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-55,82; 36,98</t>
+          <t>-53,05; 42,31</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>-3,13</t>
+          <t>-4,14</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>12,87</t>
+          <t>12,78</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4,85</t>
+          <t>4,34</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 14,95</t>
+          <t>-0,57; 15,97</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-29,01; -18,35</t>
+          <t>-29,08; -17,72</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 4,13</t>
+          <t>-10,62; 3,08</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,22; 13,44</t>
+          <t>0,12; 13,58</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-16,97; -7,43</t>
+          <t>-17,71; -7,31</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,08; 19,19</t>
+          <t>7,07; 19,33</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,0; 12,73</t>
+          <t>2,36; 12,12</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-21,93; -13,9</t>
+          <t>-21,48; -13,87</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 9,77</t>
+          <t>-0,48; 8,87</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>-12,24%</t>
+          <t>-16,2%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>78,25%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>20,71%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-2,73; 67,4</t>
+          <t>-1,64; 72,96</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-96,85; -80,56</t>
+          <t>-96,75; -80,33</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-34,63; 17,97</t>
+          <t>-35,79; 13,6</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2,49; 107,42</t>
+          <t>-0,1; 98,23</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-87,31; -53,93</t>
+          <t>-87,89; -53,81</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>32,33; 148,62</t>
+          <t>34,23; 150,01</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>8,63; 67,89</t>
+          <t>9,91; 65,29</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-90,8; -75,04</t>
+          <t>-90,86; -74,68</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 54,4</t>
+          <t>-2,05; 49,05</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,52</t>
+          <t>1,45</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>3,73</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,11</t>
+          <t>2,61</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>8,7; 17,03</t>
+          <t>8,43; 17,18</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 5,35</t>
+          <t>-2,77; 5,49</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 5,2</t>
+          <t>-2,72; 5,82</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7,87; 15,8</t>
+          <t>7,83; 16,07</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,61; 9,71</t>
+          <t>2,88; 10,18</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 4,92</t>
+          <t>0,43; 7,47</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>8,96; 15,18</t>
+          <t>9,25; 15,23</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,03; 6,7</t>
+          <t>1,12; 6,64</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 3,34</t>
+          <t>-0,03; 5,34</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>55,66; 151,89</t>
+          <t>56,4; 157,63</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-18,8; 48,42</t>
+          <t>-18,48; 50,42</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-24,97; 48,48</t>
+          <t>-18,8; 52,47</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>65,36; 191,25</t>
+          <t>68,1; 194,8</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>21,29; 113,66</t>
+          <t>24,66; 125,37</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-57,82; 52,96</t>
+          <t>2,8; 91,53</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>70,34; 151,12</t>
+          <t>71,98; 151,58</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>8,18; 66,97</t>
+          <t>8,1; 63,81</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-41,93; 31,36</t>
+          <t>-2,24; 52,18</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>13,18</t>
+          <t>21,53</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>8,78</t>
+          <t>8,47</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>11,36</t>
+          <t>14,88</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-5,9; -0,15</t>
+          <t>-6,33; -0,47</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>4,97; 12,12</t>
+          <t>4,45; 12,0</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 23,15</t>
+          <t>17,43; 26,01</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 0,46</t>
+          <t>-4,65; 0,62</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>5,73; 12,84</t>
+          <t>5,96; 12,72</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>5,88; 12,31</t>
+          <t>5,17; 11,76</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-4,53; -0,66</t>
+          <t>-4,61; -0,4</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>6,31; 11,53</t>
+          <t>6,08; 11,54</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>2,83; 15,9</t>
+          <t>12,31; 17,53</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>123,47%</t>
+          <t>201,78%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>89,96%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>113,27%</t>
+          <t>148,4%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-48,72; -1,66</t>
+          <t>-50,45; -4,51</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>41,1; 133,16</t>
+          <t>37,82; 134,2</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2,49; 228,19</t>
+          <t>137,44; 289,52</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-45,19; 6,14</t>
+          <t>-43,51; 8,34</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>48,42; 159,73</t>
+          <t>53,87; 167,37</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>53,83; 157,96</t>
+          <t>46,33; 145,83</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-41,27; -6,94</t>
+          <t>-41,06; -4,95</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>57,18; 128,39</t>
+          <t>53,8; 131,87</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>25,79; 167,81</t>
+          <t>107,79; 197,06</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>-0,3</t>
+          <t>1,26</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-0,12</t>
+          <t>0,9</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>1,06</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,05; 3,55</t>
+          <t>0,05; 3,61</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-4,13; -0,51</t>
+          <t>-4,09; -0,47</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 2,04</t>
+          <t>-0,76; 3,23</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 2,69</t>
+          <t>-0,43; 2,6</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,7</t>
+          <t>-0,56; 2,63</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 1,64</t>
+          <t>-0,43; 2,45</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,69</t>
+          <t>0,19; 2,64</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,71</t>
+          <t>-1,72; 0,65</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 1,28</t>
+          <t>-0,18; 2,35</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>-1,9%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-0,95%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>-1,62%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0,36; 23,88</t>
+          <t>0,29; 24,16</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-24,68; -3,25</t>
+          <t>-24,28; -3,17</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-22,86; 13,27</t>
+          <t>-4,45; 21,61</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 22,97</t>
+          <t>-3,31; 21,82</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 22,52</t>
+          <t>-4,13; 22,1</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-21,58; 14,04</t>
+          <t>-3,14; 21,07</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>2,17; 20,01</t>
+          <t>1,27; 19,59</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-11,48; 5,31</t>
+          <t>-11,87; 4,95</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>-15,6; 9,34</t>
+          <t>-1,32; 17,15</t>
         </is>
       </c>
     </row>
